--- a/SeaAroundUsExtraction/eez_output/regional_calculations/EEZ_512_Oman.xlsx
+++ b/SeaAroundUsExtraction/eez_output/regional_calculations/EEZ_512_Oman.xlsx
@@ -2,12 +2,12 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Species" sheetId="1" r:id="Re37ce49b6c704e30"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Commercial" sheetId="2" r:id="R893063f1a08b4013"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Functional" sheetId="3" r:id="R2d3394b5b0e041a0"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Missing TL" sheetId="4" r:id="R7848226a781446c3"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Validation" sheetId="5" r:id="R9952c3228c664b06"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Metadata" sheetId="6" r:id="Rfa423a6c175d45c4"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Species" sheetId="1" r:id="Re37114f1855649a8"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Commercial" sheetId="2" r:id="Ra3fddf2feb4a4eee"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Functional" sheetId="3" r:id="Rb57b9ba1b6574a10"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Missing TL" sheetId="4" r:id="Rbe390a6080254e59"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Validation" sheetId="5" r:id="R22d23e99e3b8496f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Metadata" sheetId="6" r:id="R4a7563c036864f6f"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -18,13 +18,11 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <x:styleSheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <x:numFmts count="6">
+  <x:numFmts count="4">
     <x:numFmt numFmtId="200" formatCode="0"/>
     <x:numFmt numFmtId="201" formatCode="#,##0.00"/>
     <x:numFmt numFmtId="202" formatCode="0.0000"/>
-    <x:numFmt numFmtId="203" formatCode="#,##0"/>
-    <x:numFmt numFmtId="204" formatCode="0.00%"/>
-    <x:numFmt numFmtId="205" formatCode="0.00"/>
+    <x:numFmt numFmtId="203" formatCode="0.00"/>
   </x:numFmts>
   <x:fonts count="7">
     <x:font>
@@ -184,7 +182,7 @@
   <x:cellStyleXfs count="1">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </x:cellStyleXfs>
-  <x:cellXfs count="37">
+  <x:cellXfs count="35">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <x:extLst>
@@ -244,8 +242,6 @@
     <x:xf numFmtId="200" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="201" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="202" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <x:xf numFmtId="203" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <x:xf numFmtId="204" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1">
       <x:extLst>
         <x:ext uri="{C7286773-470A-42A8-94C5-96B5CB345126}">
@@ -253,14 +249,14 @@
         </x:ext>
       </x:extLst>
     </x:xf>
-    <x:xf numFmtId="205" fontId="2" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <x:xf numFmtId="203" fontId="2" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment wrapText="1"/>
     </x:xf>
   </x:cellXfs>
   <x:cellStyles count="1">
     <x:cellStyle name="Normal" xfId="0"/>
   </x:cellStyles>
-  <x:dxfs count="3">
+  <x:dxfs count="1">
     <x:dxf>
       <x:font>
         <x:color rgb="FF9A3412"/>
@@ -268,28 +264,6 @@
       <x:fill>
         <x:patternFill patternType="solid">
           <x:bgColor rgb="FFFCEAD8"/>
-        </x:patternFill>
-      </x:fill>
-    </x:dxf>
-    <x:dxf>
-      <x:font>
-        <x:b/>
-        <x:color rgb="FFB42318"/>
-      </x:font>
-      <x:fill>
-        <x:patternFill patternType="solid">
-          <x:bgColor rgb="FFFEE4E2"/>
-        </x:patternFill>
-      </x:fill>
-    </x:dxf>
-    <x:dxf>
-      <x:font>
-        <x:b/>
-        <x:color rgb="FFB42318"/>
-      </x:font>
-      <x:fill>
-        <x:patternFill patternType="solid">
-          <x:bgColor rgb="FFFEE4E2"/>
         </x:patternFill>
       </x:fill>
     </x:dxf>
@@ -345,56 +319,36 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="EEZ512CommercialTable" displayName="EEZ512CommercialTable" ref="A1:O9" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
-  <x:autoFilter ref="A1:O9"/>
-  <x:tableColumns count="15">
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="EEZ512CommercialTable" displayName="EEZ512CommercialTable" ref="A1:E9" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+  <x:autoFilter ref="A1:E9"/>
+  <x:tableColumns count="5">
     <x:tableColumn id="1" name="commercial_group"/>
-    <x:tableColumn id="2" name="taxon_count_total"/>
-    <x:tableColumn id="3" name="taxon_count_matched"/>
-    <x:tableColumn id="4" name="catch_tonnes_total"/>
-    <x:tableColumn id="5" name="catch_tonnes_matched"/>
-    <x:tableColumn id="6" name="catch_tonnes_missing_tl"/>
-    <x:tableColumn id="7" name="catch_coverage_fraction"/>
-    <x:tableColumn id="8" name="sppr_correct"/>
-    <x:tableColumn id="9" name="ppr_correct"/>
-    <x:tableColumn id="10" name="tl_weighted_jensen"/>
-    <x:tableColumn id="11" name="sppr_jensen"/>
-    <x:tableColumn id="12" name="ppr_jensen"/>
-    <x:tableColumn id="13" name="jensen_difference"/>
-    <x:tableColumn id="14" name="jensen_ratio_correct_to_error"/>
-    <x:tableColumn id="15" name="jensen_percent_difference"/>
+    <x:tableColumn id="2" name="catch_tonnes_matched"/>
+    <x:tableColumn id="3" name="tl_weighted"/>
+    <x:tableColumn id="4" name="sppr"/>
+    <x:tableColumn id="5" name="ppr"/>
   </x:tableColumns>
   <x:tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </x:table>
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="EEZ512FunctionalTable" displayName="EEZ512FunctionalTable" ref="A1:O17" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
-  <x:autoFilter ref="A1:O17"/>
-  <x:tableColumns count="15">
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="EEZ512FunctionalTable" displayName="EEZ512FunctionalTable" ref="A1:E17" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+  <x:autoFilter ref="A1:E17"/>
+  <x:tableColumns count="5">
     <x:tableColumn id="1" name="functional_group"/>
-    <x:tableColumn id="2" name="taxon_count_total"/>
-    <x:tableColumn id="3" name="taxon_count_matched"/>
-    <x:tableColumn id="4" name="catch_tonnes_total"/>
-    <x:tableColumn id="5" name="catch_tonnes_matched"/>
-    <x:tableColumn id="6" name="catch_tonnes_missing_tl"/>
-    <x:tableColumn id="7" name="catch_coverage_fraction"/>
-    <x:tableColumn id="8" name="sppr_correct"/>
-    <x:tableColumn id="9" name="ppr_correct"/>
-    <x:tableColumn id="10" name="tl_weighted_jensen"/>
-    <x:tableColumn id="11" name="sppr_jensen"/>
-    <x:tableColumn id="12" name="ppr_jensen"/>
-    <x:tableColumn id="13" name="jensen_difference"/>
-    <x:tableColumn id="14" name="jensen_ratio_correct_to_error"/>
-    <x:tableColumn id="15" name="jensen_percent_difference"/>
+    <x:tableColumn id="2" name="catch_tonnes_matched"/>
+    <x:tableColumn id="3" name="tl_weighted"/>
+    <x:tableColumn id="4" name="sppr"/>
+    <x:tableColumn id="5" name="ppr"/>
   </x:tableColumns>
   <x:tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </x:table>
 </file>
 
 <file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="4" name="EEZ512ValidationTable" displayName="EEZ512ValidationTable" ref="A1:D19" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
-  <x:autoFilter ref="A1:D19"/>
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="4" name="EEZ512ValidationTable" displayName="EEZ512ValidationTable" ref="A1:D17" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+  <x:autoFilter ref="A1:D17"/>
   <x:tableColumns count="4">
     <x:tableColumn id="1" name="unit_id"/>
     <x:tableColumn id="2" name="check"/>
@@ -5116,7 +5070,7 @@
   </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R65d8a8f2a5154939"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R07cc043a62b54898"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -5126,20 +5080,10 @@
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
     <x:col min="1" max="1" width="26" hidden="0" customWidth="1"/>
-    <x:col min="2" max="2" width="22" hidden="0" customWidth="1"/>
-    <x:col min="3" max="3" width="22" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="18" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="15" hidden="0" customWidth="1"/>
     <x:col min="4" max="4" width="18" hidden="0" customWidth="1"/>
     <x:col min="5" max="5" width="18" hidden="0" customWidth="1"/>
-    <x:col min="6" max="6" width="18" hidden="0" customWidth="1"/>
-    <x:col min="7" max="7" width="16" hidden="0" customWidth="1"/>
-    <x:col min="8" max="8" width="18" hidden="0" customWidth="1"/>
-    <x:col min="9" max="9" width="18" hidden="0" customWidth="1"/>
-    <x:col min="10" max="10" width="15" hidden="0" customWidth="1"/>
-    <x:col min="11" max="11" width="18" hidden="0" customWidth="1"/>
-    <x:col min="12" max="12" width="18" hidden="0" customWidth="1"/>
-    <x:col min="13" max="13" width="18" hidden="0" customWidth="1"/>
-    <x:col min="14" max="14" width="16" hidden="0" customWidth="1"/>
-    <x:col min="15" max="15" width="16" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1" ht="32" customHeight="1">
@@ -5147,498 +5091,174 @@
         <x:v>commercial_group</x:v>
       </x:c>
       <x:c r="B1" s="29" t="str">
-        <x:v>taxon_count_total</x:v>
+        <x:v>catch_tonnes_matched</x:v>
       </x:c>
       <x:c r="C1" s="29" t="str">
-        <x:v>taxon_count_matched</x:v>
+        <x:v>tl_weighted</x:v>
       </x:c>
       <x:c r="D1" s="29" t="str">
-        <x:v>catch_tonnes_total</x:v>
+        <x:v>sppr</x:v>
       </x:c>
       <x:c r="E1" s="29" t="str">
-        <x:v>catch_tonnes_matched</x:v>
-      </x:c>
-      <x:c r="F1" s="29" t="str">
-        <x:v>catch_tonnes_missing_tl</x:v>
-      </x:c>
-      <x:c r="G1" s="29" t="str">
-        <x:v>catch_coverage_fraction</x:v>
-      </x:c>
-      <x:c r="H1" s="29" t="str">
-        <x:v>sppr_correct</x:v>
-      </x:c>
-      <x:c r="I1" s="29" t="str">
-        <x:v>ppr_correct</x:v>
-      </x:c>
-      <x:c r="J1" s="29" t="str">
-        <x:v>tl_weighted_jensen</x:v>
-      </x:c>
-      <x:c r="K1" s="29" t="str">
-        <x:v>sppr_jensen</x:v>
-      </x:c>
-      <x:c r="L1" s="29" t="str">
-        <x:v>ppr_jensen</x:v>
-      </x:c>
-      <x:c r="M1" s="29" t="str">
-        <x:v>jensen_difference</x:v>
-      </x:c>
-      <x:c r="N1" s="29" t="str">
-        <x:v>jensen_ratio_correct_to_error</x:v>
-      </x:c>
-      <x:c r="O1" s="29" t="str">
-        <x:v>jensen_percent_difference</x:v>
+        <x:v>ppr</x:v>
       </x:c>
     </x:row>
     <x:row r="2" ht="18" customHeight="1">
       <x:c r="A2" s="24" t="str">
         <x:v>Anchovies</x:v>
       </x:c>
-      <x:c r="B2" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C2" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="D2" s="31" t="n">
+      <x:c r="B2" s="31" t="n">
         <x:v>10014.8563276919</x:v>
       </x:c>
+      <x:c r="C2" s="32" t="n">
+        <x:v>3.2</x:v>
+      </x:c>
+      <x:c r="D2" s="32" t="n">
+        <x:f>IF(C2="","",(1/'Metadata'!$B$5)^(C2-1))</x:f>
+        <x:v>158.48931924611142</x:v>
+      </x:c>
       <x:c r="E2" s="31" t="n">
-        <x:v>10014.8563276919</x:v>
-      </x:c>
-      <x:c r="F2" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G2" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H2" s="32" t="n">
-        <x:f>IF(E2=0,"",I2/E2)</x:f>
-        <x:v>158.48931924611142</x:v>
-      </x:c>
-      <x:c r="I2" s="31" t="n">
-        <x:f>IF(C2=0,"",SUMIF('Species'!$H$2:$H$67,A2,'Species'!$U$2:$U$67))</x:f>
+        <x:f>IF(B2=0,"",B2*D2)</x:f>
         <x:v>1587247.7617235004</x:v>
-      </x:c>
-      <x:c r="J2" s="32" t="n">
-        <x:v>3.2</x:v>
-      </x:c>
-      <x:c r="K2" s="32" t="n">
-        <x:f>IF(J2="","",(1/'Metadata'!$B$5)^(J2-1))</x:f>
-        <x:v>158.48931924611142</x:v>
-      </x:c>
-      <x:c r="L2" s="31" t="n">
-        <x:f>IF(E2=0,"",E2*K2)</x:f>
-        <x:v>1587247.7617235004</x:v>
-      </x:c>
-      <x:c r="M2" s="31" t="n">
-        <x:f>IF(E2=0,"",I2-L2)</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="N2" s="32" t="n">
-        <x:f>IF(L2=0,"",I2/L2)</x:f>
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="O2" s="34" t="n">
-        <x:f>IF(L2=0,"",M2/L2)</x:f>
-        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="3" ht="18" customHeight="1">
       <x:c r="A3" s="24" t="str">
         <x:v>Crustaceans</x:v>
       </x:c>
-      <x:c r="B3" s="33" t="n">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C3" s="33" t="n">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="D3" s="31" t="n">
+      <x:c r="B3" s="31" t="n">
         <x:v>2954.200885152</x:v>
       </x:c>
+      <x:c r="C3" s="32" t="n">
+        <x:v>3.182798411916014</x:v>
+      </x:c>
+      <x:c r="D3" s="32" t="n">
+        <x:f>IF(C3="","",(1/'Metadata'!$B$5)^(C3-1))</x:f>
+        <x:v>152.33454927241874</x:v>
+      </x:c>
       <x:c r="E3" s="31" t="n">
-        <x:v>2954.200885152</x:v>
-      </x:c>
-      <x:c r="F3" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G3" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H3" s="32" t="n">
-        <x:f>IF(E3=0,"",I3/E3)</x:f>
-        <x:v>157.7997260290634</x:v>
-      </x:c>
-      <x:c r="I3" s="31" t="n">
-        <x:f>IF(C3=0,"",SUMIF('Species'!$H$2:$H$67,A3,'Species'!$U$2:$U$67))</x:f>
-        <x:v>466172.09031180217</x:v>
-      </x:c>
-      <x:c r="J3" s="32" t="n">
-        <x:v>3.182798411916014</x:v>
-      </x:c>
-      <x:c r="K3" s="32" t="n">
-        <x:f>IF(J3="","",(1/'Metadata'!$B$5)^(J3-1))</x:f>
-        <x:v>152.33454927241874</x:v>
-      </x:c>
-      <x:c r="L3" s="31" t="n">
-        <x:f>IF(E3=0,"",E3*K3)</x:f>
+        <x:f>IF(B3=0,"",B3*D3)</x:f>
         <x:v>450026.8602998104</x:v>
-      </x:c>
-      <x:c r="M3" s="31" t="n">
-        <x:f>IF(E3=0,"",I3-L3)</x:f>
-        <x:v>16145.230011991749</x:v>
-      </x:c>
-      <x:c r="N3" s="32" t="n">
-        <x:f>IF(L3=0,"",I3/L3)</x:f>
-        <x:v>1.035876147484254</x:v>
-      </x:c>
-      <x:c r="O3" s="34" t="n">
-        <x:f>IF(L3=0,"",M3/L3)</x:f>
-        <x:v>0.035876147484253954</x:v>
       </x:c>
     </x:row>
     <x:row r="4" ht="18" customHeight="1">
       <x:c r="A4" s="24" t="str">
         <x:v>Herring-likes</x:v>
       </x:c>
-      <x:c r="B4" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="C4" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="D4" s="31" t="n">
+      <x:c r="B4" s="31" t="n">
         <x:v>145971.31363687257</x:v>
       </x:c>
+      <x:c r="C4" s="32" t="n">
+        <x:v>2.470352375943453</x:v>
+      </x:c>
+      <x:c r="D4" s="32" t="n">
+        <x:f>IF(C4="","",(1/'Metadata'!$B$5)^(C4-1))</x:f>
+        <x:v>29.53604737505334</x:v>
+      </x:c>
       <x:c r="E4" s="31" t="n">
-        <x:v>145971.31363687257</x:v>
-      </x:c>
-      <x:c r="F4" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G4" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H4" s="32" t="n">
-        <x:f>IF(E4=0,"",I4/E4)</x:f>
-        <x:v>35.266994519310344</x:v>
-      </x:c>
-      <x:c r="I4" s="31" t="n">
-        <x:f>IF(C4=0,"",SUMIF('Species'!$H$2:$H$67,A4,'Species'!$U$2:$U$67))</x:f>
-        <x:v>5147969.518008116</x:v>
-      </x:c>
-      <x:c r="J4" s="32" t="n">
-        <x:v>2.470352375943453</x:v>
-      </x:c>
-      <x:c r="K4" s="32" t="n">
-        <x:f>IF(J4="","",(1/'Metadata'!$B$5)^(J4-1))</x:f>
-        <x:v>29.53604737505334</x:v>
-      </x:c>
-      <x:c r="L4" s="31" t="n">
-        <x:f>IF(E4=0,"",E4*K4)</x:f>
+        <x:f>IF(B4=0,"",B4*D4)</x:f>
         <x:v>4311415.634977438</x:v>
-      </x:c>
-      <x:c r="M4" s="31" t="n">
-        <x:f>IF(E4=0,"",I4-L4)</x:f>
-        <x:v>836553.8830306781</x:v>
-      </x:c>
-      <x:c r="N4" s="32" t="n">
-        <x:f>IF(L4=0,"",I4/L4)</x:f>
-        <x:v>1.1940322979403621</x:v>
-      </x:c>
-      <x:c r="O4" s="34" t="n">
-        <x:f>IF(L4=0,"",M4/L4)</x:f>
-        <x:v>0.19403229794036222</x:v>
       </x:c>
     </x:row>
     <x:row r="5" ht="18" customHeight="1">
       <x:c r="A5" s="24" t="str">
         <x:v>Molluscs</x:v>
       </x:c>
-      <x:c r="B5" s="33" t="n">
+      <x:c r="B5" s="31" t="n">
+        <x:v>15.6414576048</x:v>
+      </x:c>
+      <x:c r="C5" s="32" t="n">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="C5" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="D5" s="31" t="n">
-        <x:v>15.6414576048</x:v>
+      <x:c r="D5" s="32" t="n">
+        <x:f>IF(C5="","",(1/'Metadata'!$B$5)^(C5-1))</x:f>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="E5" s="31" t="n">
-        <x:v>15.6414576048</x:v>
-      </x:c>
-      <x:c r="F5" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G5" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H5" s="32" t="n">
-        <x:f>IF(E5=0,"",I5/E5)</x:f>
-        <x:v>10.000000000000002</x:v>
-      </x:c>
-      <x:c r="I5" s="31" t="n">
-        <x:f>IF(C5=0,"",SUMIF('Species'!$H$2:$H$67,A5,'Species'!$U$2:$U$67))</x:f>
-        <x:v>156.41457604800001</x:v>
-      </x:c>
-      <x:c r="J5" s="32" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="K5" s="32" t="n">
-        <x:f>IF(J5="","",(1/'Metadata'!$B$5)^(J5-1))</x:f>
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="L5" s="31" t="n">
-        <x:f>IF(E5=0,"",E5*K5)</x:f>
+        <x:f>IF(B5=0,"",B5*D5)</x:f>
         <x:v>156.414576048</x:v>
-      </x:c>
-      <x:c r="M5" s="31" t="n">
-        <x:f>IF(E5=0,"",I5-L5)</x:f>
-        <x:v>2.842170943040401e-14</x:v>
-      </x:c>
-      <x:c r="N5" s="32" t="n">
-        <x:f>IF(L5=0,"",I5/L5)</x:f>
-        <x:v>1.0000000000000002</x:v>
-      </x:c>
-      <x:c r="O5" s="34" t="n">
-        <x:f>IF(L5=0,"",M5/L5)</x:f>
-        <x:v>1.8170755020735438e-16</x:v>
       </x:c>
     </x:row>
     <x:row r="6" ht="18" customHeight="1">
       <x:c r="A6" s="24" t="str">
         <x:v>Other fishes &amp; inverts</x:v>
       </x:c>
-      <x:c r="B6" s="33" t="n">
-        <x:v>6</x:v>
-      </x:c>
-      <x:c r="C6" s="33" t="n">
-        <x:v>6</x:v>
-      </x:c>
-      <x:c r="D6" s="31" t="n">
+      <x:c r="B6" s="31" t="n">
         <x:v>36197.4964595183</x:v>
       </x:c>
+      <x:c r="C6" s="32" t="n">
+        <x:v>3.410455353355738</x:v>
+      </x:c>
+      <x:c r="D6" s="32" t="n">
+        <x:f>IF(C6="","",(1/'Metadata'!$B$5)^(C6-1))</x:f>
+        <x:v>257.3092230006678</x:v>
+      </x:c>
       <x:c r="E6" s="31" t="n">
-        <x:v>36197.4964595183</x:v>
-      </x:c>
-      <x:c r="F6" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G6" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H6" s="32" t="n">
-        <x:f>IF(E6=0,"",I6/E6)</x:f>
-        <x:v>291.7836800592163</x:v>
-      </x:c>
-      <x:c r="I6" s="31" t="n">
-        <x:f>IF(C6=0,"",SUMIF('Species'!$H$2:$H$67,A6,'Species'!$U$2:$U$67))</x:f>
-        <x:v>10561838.725888701</x:v>
-      </x:c>
-      <x:c r="J6" s="32" t="n">
-        <x:v>3.410455353355738</x:v>
-      </x:c>
-      <x:c r="K6" s="32" t="n">
-        <x:f>IF(J6="","",(1/'Metadata'!$B$5)^(J6-1))</x:f>
-        <x:v>257.3092230006678</x:v>
-      </x:c>
-      <x:c r="L6" s="31" t="n">
-        <x:f>IF(E6=0,"",E6*K6)</x:f>
+        <x:f>IF(B6=0,"",B6*D6)</x:f>
         <x:v>9313949.688568078</x:v>
-      </x:c>
-      <x:c r="M6" s="31" t="n">
-        <x:f>IF(E6=0,"",I6-L6)</x:f>
-        <x:v>1247889.0373206232</x:v>
-      </x:c>
-      <x:c r="N6" s="32" t="n">
-        <x:f>IF(L6=0,"",I6/L6)</x:f>
-        <x:v>1.1339806504272059</x:v>
-      </x:c>
-      <x:c r="O6" s="34" t="n">
-        <x:f>IF(L6=0,"",M6/L6)</x:f>
-        <x:v>0.13398065042720592</x:v>
       </x:c>
     </x:row>
     <x:row r="7" ht="18" customHeight="1">
       <x:c r="A7" s="24" t="str">
         <x:v>Perch-likes</x:v>
       </x:c>
-      <x:c r="B7" s="33" t="n">
-        <x:v>26</x:v>
-      </x:c>
-      <x:c r="C7" s="33" t="n">
-        <x:v>26</x:v>
-      </x:c>
-      <x:c r="D7" s="31" t="n">
+      <x:c r="B7" s="31" t="n">
         <x:v>73941.6077893722</x:v>
       </x:c>
+      <x:c r="C7" s="32" t="n">
+        <x:v>3.8404926535064723</x:v>
+      </x:c>
+      <x:c r="D7" s="32" t="n">
+        <x:f>IF(C7="","",(1/'Metadata'!$B$5)^(C7-1))</x:f>
+        <x:v>692.6162130933258</x:v>
+      </x:c>
       <x:c r="E7" s="31" t="n">
-        <x:v>73941.6077893722</x:v>
-      </x:c>
-      <x:c r="F7" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G7" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H7" s="32" t="n">
-        <x:f>IF(E7=0,"",I7/E7)</x:f>
-        <x:v>1056.0375450908496</x:v>
-      </x:c>
-      <x:c r="I7" s="31" t="n">
-        <x:f>IF(C7=0,"",SUMIF('Species'!$H$2:$H$67,A7,'Species'!$U$2:$U$67))</x:f>
-        <x:v>78085113.96995905</x:v>
-      </x:c>
-      <x:c r="J7" s="32" t="n">
-        <x:v>3.8404926535064723</x:v>
-      </x:c>
-      <x:c r="K7" s="32" t="n">
-        <x:f>IF(J7="","",(1/'Metadata'!$B$5)^(J7-1))</x:f>
-        <x:v>692.6162130933258</x:v>
-      </x:c>
-      <x:c r="L7" s="31" t="n">
-        <x:f>IF(E7=0,"",E7*K7)</x:f>
+        <x:f>IF(B7=0,"",B7*D7)</x:f>
         <x:v>51213156.37710693</x:v>
-      </x:c>
-      <x:c r="M7" s="31" t="n">
-        <x:f>IF(E7=0,"",I7-L7)</x:f>
-        <x:v>26871957.592852123</x:v>
-      </x:c>
-      <x:c r="N7" s="32" t="n">
-        <x:f>IF(L7=0,"",I7/L7)</x:f>
-        <x:v>1.5247080924866467</x:v>
-      </x:c>
-      <x:c r="O7" s="34" t="n">
-        <x:f>IF(L7=0,"",M7/L7)</x:f>
-        <x:v>0.5247080924866467</x:v>
       </x:c>
     </x:row>
     <x:row r="8" ht="18" customHeight="1">
       <x:c r="A8" s="24" t="str">
         <x:v>Sharks &amp; rays</x:v>
       </x:c>
-      <x:c r="B8" s="33" t="n">
-        <x:v>12</x:v>
-      </x:c>
-      <x:c r="C8" s="33" t="n">
-        <x:v>12</x:v>
-      </x:c>
-      <x:c r="D8" s="31" t="n">
+      <x:c r="B8" s="31" t="n">
         <x:v>3697.0233802766998</x:v>
       </x:c>
+      <x:c r="C8" s="32" t="n">
+        <x:v>4.051479916872144</x:v>
+      </x:c>
+      <x:c r="D8" s="32" t="n">
+        <x:f>IF(C8="","",(1/'Metadata'!$B$5)^(C8-1))</x:f>
+        <x:v>1125.848404958591</x:v>
+      </x:c>
       <x:c r="E8" s="31" t="n">
-        <x:v>3697.0233802766998</x:v>
-      </x:c>
-      <x:c r="F8" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G8" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H8" s="32" t="n">
-        <x:f>IF(E8=0,"",I8/E8)</x:f>
-        <x:v>1128.2024493772308</x:v>
-      </x:c>
-      <x:c r="I8" s="31" t="n">
-        <x:f>IF(C8=0,"",SUMIF('Species'!$H$2:$H$67,A8,'Species'!$U$2:$U$67))</x:f>
-        <x:v>4170990.833033062</x:v>
-      </x:c>
-      <x:c r="J8" s="32" t="n">
-        <x:v>4.051479916872144</x:v>
-      </x:c>
-      <x:c r="K8" s="32" t="n">
-        <x:f>IF(J8="","",(1/'Metadata'!$B$5)^(J8-1))</x:f>
-        <x:v>1125.848404958591</x:v>
-      </x:c>
-      <x:c r="L8" s="31" t="n">
-        <x:f>IF(E8=0,"",E8*K8)</x:f>
+        <x:f>IF(B8=0,"",B8*D8)</x:f>
         <x:v>4162287.8757791403</x:v>
-      </x:c>
-      <x:c r="M8" s="31" t="n">
-        <x:f>IF(E8=0,"",I8-L8)</x:f>
-        <x:v>8702.957253921777</x:v>
-      </x:c>
-      <x:c r="N8" s="32" t="n">
-        <x:f>IF(L8=0,"",I8/L8)</x:f>
-        <x:v>1.0020909070957262</x:v>
-      </x:c>
-      <x:c r="O8" s="34" t="n">
-        <x:f>IF(L8=0,"",M8/L8)</x:f>
-        <x:v>0.00209090709572621</x:v>
       </x:c>
     </x:row>
     <x:row r="9" ht="18" customHeight="1">
       <x:c r="A9" s="24" t="str">
         <x:v>Tuna &amp; billfishes</x:v>
       </x:c>
-      <x:c r="B9" s="33" t="n">
-        <x:v>13</x:v>
-      </x:c>
-      <x:c r="C9" s="33" t="n">
-        <x:v>13</x:v>
-      </x:c>
-      <x:c r="D9" s="31" t="n">
+      <x:c r="B9" s="31" t="n">
         <x:v>31526.301779619407</x:v>
       </x:c>
+      <x:c r="C9" s="32" t="n">
+        <x:v>4.437737311418903</x:v>
+      </x:c>
+      <x:c r="D9" s="32" t="n">
+        <x:f>IF(C9="","",(1/'Metadata'!$B$5)^(C9-1))</x:f>
+        <x:v>2739.916397081589</x:v>
+      </x:c>
       <x:c r="E9" s="31" t="n">
-        <x:v>31526.301779619407</x:v>
-      </x:c>
-      <x:c r="F9" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G9" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H9" s="32" t="n">
-        <x:f>IF(E9=0,"",I9/E9)</x:f>
-        <x:v>2759.249441005003</x:v>
-      </x:c>
-      <x:c r="I9" s="31" t="n">
-        <x:f>IF(C9=0,"",SUMIF('Species'!$H$2:$H$67,A9,'Species'!$U$2:$U$67))</x:f>
-        <x:v>86988930.56236988</x:v>
-      </x:c>
-      <x:c r="J9" s="32" t="n">
-        <x:v>4.437737311418903</x:v>
-      </x:c>
-      <x:c r="K9" s="32" t="n">
-        <x:f>IF(J9="","",(1/'Metadata'!$B$5)^(J9-1))</x:f>
-        <x:v>2739.916397081589</x:v>
-      </x:c>
-      <x:c r="L9" s="31" t="n">
-        <x:f>IF(E9=0,"",E9*K9)</x:f>
+        <x:f>IF(B9=0,"",B9*D9)</x:f>
         <x:v>86379431.18532169</x:v>
       </x:c>
-      <x:c r="M9" s="31" t="n">
-        <x:f>IF(E9=0,"",I9-L9)</x:f>
-        <x:v>609499.3770481944</x:v>
-      </x:c>
-      <x:c r="N9" s="32" t="n">
-        <x:f>IF(L9=0,"",I9/L9)</x:f>
-        <x:v>1.0070560707414309</x:v>
-      </x:c>
-      <x:c r="O9" s="34" t="n">
-        <x:f>IF(L9=0,"",M9/L9)</x:f>
-        <x:v>0.0070560707414309256</x:v>
-      </x:c>
     </x:row>
   </x:sheetData>
-  <x:conditionalFormatting sqref="G2:G9">
-    <x:cfRule type="cellIs" dxfId="1" priority="1" operator="lessThan">
-      <x:formula>0.9</x:formula>
-    </x:cfRule>
-  </x:conditionalFormatting>
-  <x:conditionalFormatting sqref="O2:O9">
-    <x:cfRule type="dataBar" priority="2">
-      <x:dataBar>
-        <x:cfvo type="min"/>
-        <x:cfvo type="max"/>
-        <x:color rgb="FFE28A32"/>
-      </x:dataBar>
-    </x:cfRule>
-  </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R37572968e5814747"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rfae56a18fe074fbe"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -5648,20 +5268,10 @@
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
     <x:col min="1" max="1" width="34" hidden="0" customWidth="1"/>
-    <x:col min="2" max="2" width="22" hidden="0" customWidth="1"/>
-    <x:col min="3" max="3" width="22" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="18" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="15" hidden="0" customWidth="1"/>
     <x:col min="4" max="4" width="18" hidden="0" customWidth="1"/>
     <x:col min="5" max="5" width="18" hidden="0" customWidth="1"/>
-    <x:col min="6" max="6" width="18" hidden="0" customWidth="1"/>
-    <x:col min="7" max="7" width="16" hidden="0" customWidth="1"/>
-    <x:col min="8" max="8" width="18" hidden="0" customWidth="1"/>
-    <x:col min="9" max="9" width="18" hidden="0" customWidth="1"/>
-    <x:col min="10" max="10" width="15" hidden="0" customWidth="1"/>
-    <x:col min="11" max="11" width="18" hidden="0" customWidth="1"/>
-    <x:col min="12" max="12" width="18" hidden="0" customWidth="1"/>
-    <x:col min="13" max="13" width="18" hidden="0" customWidth="1"/>
-    <x:col min="14" max="14" width="16" hidden="0" customWidth="1"/>
-    <x:col min="15" max="15" width="16" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1" ht="32" customHeight="1">
@@ -5669,930 +5279,326 @@
         <x:v>functional_group</x:v>
       </x:c>
       <x:c r="B1" s="29" t="str">
-        <x:v>taxon_count_total</x:v>
+        <x:v>catch_tonnes_matched</x:v>
       </x:c>
       <x:c r="C1" s="29" t="str">
-        <x:v>taxon_count_matched</x:v>
+        <x:v>tl_weighted</x:v>
       </x:c>
       <x:c r="D1" s="29" t="str">
-        <x:v>catch_tonnes_total</x:v>
+        <x:v>sppr</x:v>
       </x:c>
       <x:c r="E1" s="29" t="str">
-        <x:v>catch_tonnes_matched</x:v>
-      </x:c>
-      <x:c r="F1" s="29" t="str">
-        <x:v>catch_tonnes_missing_tl</x:v>
-      </x:c>
-      <x:c r="G1" s="29" t="str">
-        <x:v>catch_coverage_fraction</x:v>
-      </x:c>
-      <x:c r="H1" s="29" t="str">
-        <x:v>sppr_correct</x:v>
-      </x:c>
-      <x:c r="I1" s="29" t="str">
-        <x:v>ppr_correct</x:v>
-      </x:c>
-      <x:c r="J1" s="29" t="str">
-        <x:v>tl_weighted_jensen</x:v>
-      </x:c>
-      <x:c r="K1" s="29" t="str">
-        <x:v>sppr_jensen</x:v>
-      </x:c>
-      <x:c r="L1" s="29" t="str">
-        <x:v>ppr_jensen</x:v>
-      </x:c>
-      <x:c r="M1" s="29" t="str">
-        <x:v>jensen_difference</x:v>
-      </x:c>
-      <x:c r="N1" s="29" t="str">
-        <x:v>jensen_ratio_correct_to_error</x:v>
-      </x:c>
-      <x:c r="O1" s="29" t="str">
-        <x:v>jensen_percent_difference</x:v>
+        <x:v>ppr</x:v>
       </x:c>
     </x:row>
     <x:row r="2" ht="18" customHeight="1">
       <x:c r="A2" s="24" t="str">
         <x:v>Cephalopods</x:v>
       </x:c>
-      <x:c r="B2" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="C2" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="D2" s="31" t="n">
+      <x:c r="B2" s="31" t="n">
         <x:v>6872.8820506927</x:v>
       </x:c>
+      <x:c r="C2" s="32" t="n">
+        <x:v>3.7896993187771657</x:v>
+      </x:c>
+      <x:c r="D2" s="32" t="n">
+        <x:f>IF(C2="","",(1/'Metadata'!$B$5)^(C2-1))</x:f>
+        <x:v>616.1682536942997</x:v>
+      </x:c>
       <x:c r="E2" s="31" t="n">
-        <x:v>6872.8820506927</x:v>
-      </x:c>
-      <x:c r="F2" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G2" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H2" s="32" t="n">
-        <x:f>IF(E2=0,"",I2/E2)</x:f>
-        <x:v>618.9647674086917</x:v>
-      </x:c>
-      <x:c r="I2" s="31" t="n">
-        <x:f>IF(C2=0,"",SUMIF('Species'!$G$2:$G$67,A2,'Species'!$U$2:$U$67))</x:f>
-        <x:v>4254071.83993438</x:v>
-      </x:c>
-      <x:c r="J2" s="32" t="n">
-        <x:v>3.7896993187771657</x:v>
-      </x:c>
-      <x:c r="K2" s="32" t="n">
-        <x:f>IF(J2="","",(1/'Metadata'!$B$5)^(J2-1))</x:f>
-        <x:v>616.1682536942997</x:v>
-      </x:c>
-      <x:c r="L2" s="31" t="n">
-        <x:f>IF(E2=0,"",E2*K2)</x:f>
+        <x:f>IF(B2=0,"",B2*D2)</x:f>
         <x:v>4234851.731022218</x:v>
-      </x:c>
-      <x:c r="M2" s="31" t="n">
-        <x:f>IF(E2=0,"",I2-L2)</x:f>
-        <x:v>19220.10891216155</x:v>
-      </x:c>
-      <x:c r="N2" s="32" t="n">
-        <x:f>IF(L2=0,"",I2/L2)</x:f>
-        <x:v>1.004538555333913</x:v>
-      </x:c>
-      <x:c r="O2" s="34" t="n">
-        <x:f>IF(L2=0,"",M2/L2)</x:f>
-        <x:v>0.004538555333912991</x:v>
       </x:c>
     </x:row>
     <x:row r="3" ht="18" customHeight="1">
       <x:c r="A3" s="24" t="str">
         <x:v>Large demersals (&gt;=90 cm)</x:v>
       </x:c>
-      <x:c r="B3" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C3" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="D3" s="31" t="n">
+      <x:c r="B3" s="31" t="n">
         <x:v>3662.557102725</x:v>
       </x:c>
+      <x:c r="C3" s="32" t="n">
+        <x:v>3.54</x:v>
+      </x:c>
+      <x:c r="D3" s="32" t="n">
+        <x:f>IF(C3="","",(1/'Metadata'!$B$5)^(C3-1))</x:f>
+        <x:v>346.73685045253166</x:v>
+      </x:c>
       <x:c r="E3" s="31" t="n">
-        <x:v>3662.557102725</x:v>
-      </x:c>
-      <x:c r="F3" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G3" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H3" s="32" t="n">
-        <x:f>IF(E3=0,"",I3/E3)</x:f>
-        <x:v>346.73685045253166</x:v>
-      </x:c>
-      <x:c r="I3" s="31" t="n">
-        <x:f>IF(C3=0,"",SUMIF('Species'!$G$2:$G$67,A3,'Species'!$U$2:$U$67))</x:f>
+        <x:f>IF(B3=0,"",B3*D3)</x:f>
         <x:v>1269943.5144014158</x:v>
-      </x:c>
-      <x:c r="J3" s="32" t="n">
-        <x:v>3.54</x:v>
-      </x:c>
-      <x:c r="K3" s="32" t="n">
-        <x:f>IF(J3="","",(1/'Metadata'!$B$5)^(J3-1))</x:f>
-        <x:v>346.73685045253166</x:v>
-      </x:c>
-      <x:c r="L3" s="31" t="n">
-        <x:f>IF(E3=0,"",E3*K3)</x:f>
-        <x:v>1269943.5144014158</x:v>
-      </x:c>
-      <x:c r="M3" s="31" t="n">
-        <x:f>IF(E3=0,"",I3-L3)</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="N3" s="32" t="n">
-        <x:f>IF(L3=0,"",I3/L3)</x:f>
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="O3" s="34" t="n">
-        <x:f>IF(L3=0,"",M3/L3)</x:f>
-        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="4" ht="18" customHeight="1">
       <x:c r="A4" s="24" t="str">
         <x:v>Large pelagics (&gt;=90 cm)</x:v>
       </x:c>
-      <x:c r="B4" s="33" t="n">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="C4" s="33" t="n">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="D4" s="31" t="n">
+      <x:c r="B4" s="31" t="n">
         <x:v>35991.221397398804</x:v>
       </x:c>
+      <x:c r="C4" s="32" t="n">
+        <x:v>4.434024745284611</x:v>
+      </x:c>
+      <x:c r="D4" s="32" t="n">
+        <x:f>IF(C4="","",(1/'Metadata'!$B$5)^(C4-1))</x:f>
+        <x:v>2716.5940508606855</x:v>
+      </x:c>
       <x:c r="E4" s="31" t="n">
-        <x:v>35991.221397398804</x:v>
-      </x:c>
-      <x:c r="F4" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G4" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H4" s="32" t="n">
-        <x:f>IF(E4=0,"",I4/E4)</x:f>
-        <x:v>2739.491022137596</x:v>
-      </x:c>
-      <x:c r="I4" s="31" t="n">
-        <x:f>IF(C4=0,"",SUMIF('Species'!$G$2:$G$67,A4,'Species'!$U$2:$U$67))</x:f>
-        <x:v>98597627.89394055</x:v>
-      </x:c>
-      <x:c r="J4" s="32" t="n">
-        <x:v>4.434024745284611</x:v>
-      </x:c>
-      <x:c r="K4" s="32" t="n">
-        <x:f>IF(J4="","",(1/'Metadata'!$B$5)^(J4-1))</x:f>
-        <x:v>2716.5940508606855</x:v>
-      </x:c>
-      <x:c r="L4" s="31" t="n">
-        <x:f>IF(E4=0,"",E4*K4)</x:f>
+        <x:f>IF(B4=0,"",B4*D4)</x:f>
         <x:v>97773537.9313834</x:v>
-      </x:c>
-      <x:c r="M4" s="31" t="n">
-        <x:f>IF(E4=0,"",I4-L4)</x:f>
-        <x:v>824089.9625571519</x:v>
-      </x:c>
-      <x:c r="N4" s="32" t="n">
-        <x:f>IF(L4=0,"",I4/L4)</x:f>
-        <x:v>1.0084285582785752</x:v>
-      </x:c>
-      <x:c r="O4" s="34" t="n">
-        <x:f>IF(L4=0,"",M4/L4)</x:f>
-        <x:v>0.00842855827857524</x:v>
       </x:c>
     </x:row>
     <x:row r="5" ht="18" customHeight="1">
       <x:c r="A5" s="24" t="str">
         <x:v>Large rays (&gt;=90 cm)</x:v>
       </x:c>
-      <x:c r="B5" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="C5" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="D5" s="31" t="n">
+      <x:c r="B5" s="31" t="n">
         <x:v>1.3344194391</x:v>
       </x:c>
+      <x:c r="C5" s="32" t="n">
+        <x:v>3.5770605766574826</x:v>
+      </x:c>
+      <x:c r="D5" s="32" t="n">
+        <x:f>IF(C5="","",(1/'Metadata'!$B$5)^(C5-1))</x:f>
+        <x:v>377.6248594658713</x:v>
+      </x:c>
       <x:c r="E5" s="31" t="n">
-        <x:v>1.3344194391</x:v>
-      </x:c>
-      <x:c r="F5" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G5" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H5" s="32" t="n">
-        <x:f>IF(E5=0,"",I5/E5)</x:f>
-        <x:v>379.3245073165004</x:v>
-      </x:c>
-      <x:c r="I5" s="31" t="n">
-        <x:f>IF(C5=0,"",SUMIF('Species'!$G$2:$G$67,A5,'Species'!$U$2:$U$67))</x:f>
-        <x:v>506.17799629016827</x:v>
-      </x:c>
-      <x:c r="J5" s="32" t="n">
-        <x:v>3.5770605766574826</x:v>
-      </x:c>
-      <x:c r="K5" s="32" t="n">
-        <x:f>IF(J5="","",(1/'Metadata'!$B$5)^(J5-1))</x:f>
-        <x:v>377.6248594658713</x:v>
-      </x:c>
-      <x:c r="L5" s="31" t="n">
-        <x:f>IF(E5=0,"",E5*K5)</x:f>
+        <x:f>IF(B5=0,"",B5*D5)</x:f>
         <x:v>503.9099531586643</x:v>
-      </x:c>
-      <x:c r="M5" s="31" t="n">
-        <x:f>IF(E5=0,"",I5-L5)</x:f>
-        <x:v>2.268043131503987</x:v>
-      </x:c>
-      <x:c r="N5" s="32" t="n">
-        <x:f>IF(L5=0,"",I5/L5)</x:f>
-        <x:v>1.0045008897269982</x:v>
-      </x:c>
-      <x:c r="O5" s="34" t="n">
-        <x:f>IF(L5=0,"",M5/L5)</x:f>
-        <x:v>0.004500889726998221</x:v>
       </x:c>
     </x:row>
     <x:row r="6" ht="18" customHeight="1">
       <x:c r="A6" s="24" t="str">
         <x:v>Large sharks (&gt;=90 cm)</x:v>
       </x:c>
-      <x:c r="B6" s="33" t="n">
-        <x:v>9</x:v>
-      </x:c>
-      <x:c r="C6" s="33" t="n">
-        <x:v>9</x:v>
-      </x:c>
-      <x:c r="D6" s="31" t="n">
+      <x:c r="B6" s="31" t="n">
         <x:v>3695.5684836561995</x:v>
       </x:c>
+      <x:c r="C6" s="32" t="n">
+        <x:v>4.05165616154632</x:v>
+      </x:c>
+      <x:c r="D6" s="32" t="n">
+        <x:f>IF(C6="","",(1/'Metadata'!$B$5)^(C6-1))</x:f>
+        <x:v>1126.3053876310182</x:v>
+      </x:c>
       <x:c r="E6" s="31" t="n">
-        <x:v>3695.5684836561995</x:v>
-      </x:c>
-      <x:c r="F6" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G6" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H6" s="32" t="n">
-        <x:f>IF(E6=0,"",I6/E6)</x:f>
-        <x:v>1128.4837434493934</x:v>
-      </x:c>
-      <x:c r="I6" s="31" t="n">
-        <x:f>IF(C6=0,"",SUMIF('Species'!$G$2:$G$67,A6,'Species'!$U$2:$U$67))</x:f>
-        <x:v>4170388.956609946</x:v>
-      </x:c>
-      <x:c r="J6" s="32" t="n">
-        <x:v>4.05165616154632</x:v>
-      </x:c>
-      <x:c r="K6" s="32" t="n">
-        <x:f>IF(J6="","",(1/'Metadata'!$B$5)^(J6-1))</x:f>
-        <x:v>1126.3053876310182</x:v>
-      </x:c>
-      <x:c r="L6" s="31" t="n">
-        <x:f>IF(E6=0,"",E6*K6)</x:f>
+        <x:f>IF(B6=0,"",B6*D6)</x:f>
         <x:v>4162338.69350137</x:v>
-      </x:c>
-      <x:c r="M6" s="31" t="n">
-        <x:f>IF(E6=0,"",I6-L6)</x:f>
-        <x:v>8050.263108576182</x:v>
-      </x:c>
-      <x:c r="N6" s="32" t="n">
-        <x:f>IF(L6=0,"",I6/L6)</x:f>
-        <x:v>1.0019340720929666</x:v>
-      </x:c>
-      <x:c r="O6" s="34" t="n">
-        <x:f>IF(L6=0,"",M6/L6)</x:f>
-        <x:v>0.0019340720929666298</x:v>
       </x:c>
     </x:row>
     <x:row r="7" ht="18" customHeight="1">
       <x:c r="A7" s="24" t="str">
         <x:v>Lobsters, crabs</x:v>
       </x:c>
-      <x:c r="B7" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="C7" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="D7" s="31" t="n">
+      <x:c r="B7" s="31" t="n">
         <x:v>2423.556402241</x:v>
       </x:c>
+      <x:c r="C7" s="32" t="n">
+        <x:v>3.179901559029841</x:v>
+      </x:c>
+      <x:c r="D7" s="32" t="n">
+        <x:f>IF(C7="","",(1/'Metadata'!$B$5)^(C7-1))</x:f>
+        <x:v>151.3218210339342</x:v>
+      </x:c>
       <x:c r="E7" s="31" t="n">
-        <x:v>2423.556402241</x:v>
-      </x:c>
-      <x:c r="F7" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G7" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H7" s="32" t="n">
-        <x:f>IF(E7=0,"",I7/E7)</x:f>
-        <x:v>153.94818240761455</x:v>
-      </x:c>
-      <x:c r="I7" s="31" t="n">
-        <x:f>IF(C7=0,"",SUMIF('Species'!$G$2:$G$67,A7,'Species'!$U$2:$U$67))</x:f>
-        <x:v>373102.1030873395</x:v>
-      </x:c>
-      <x:c r="J7" s="32" t="n">
-        <x:v>3.179901559029841</x:v>
-      </x:c>
-      <x:c r="K7" s="32" t="n">
-        <x:f>IF(J7="","",(1/'Metadata'!$B$5)^(J7-1))</x:f>
-        <x:v>151.3218210339342</x:v>
-      </x:c>
-      <x:c r="L7" s="31" t="n">
-        <x:f>IF(E7=0,"",E7*K7)</x:f>
+        <x:f>IF(B7=0,"",B7*D7)</x:f>
         <x:v>366736.96816555806</x:v>
-      </x:c>
-      <x:c r="M7" s="31" t="n">
-        <x:f>IF(E7=0,"",I7-L7)</x:f>
-        <x:v>6365.134921781428</x:v>
-      </x:c>
-      <x:c r="N7" s="32" t="n">
-        <x:f>IF(L7=0,"",I7/L7)</x:f>
-        <x:v>1.0173561311629429</x:v>
-      </x:c>
-      <x:c r="O7" s="34" t="n">
-        <x:f>IF(L7=0,"",M7/L7)</x:f>
-        <x:v>0.017356131162942864</x:v>
       </x:c>
     </x:row>
     <x:row r="8" ht="18" customHeight="1">
       <x:c r="A8" s="24" t="str">
         <x:v>Medium benthopelagics (30 - 89 cm)</x:v>
       </x:c>
-      <x:c r="B8" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C8" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="D8" s="31" t="n">
+      <x:c r="B8" s="31" t="n">
         <x:v>4881.6432054599</x:v>
       </x:c>
+      <x:c r="C8" s="32" t="n">
+        <x:v>3.31</x:v>
+      </x:c>
+      <x:c r="D8" s="32" t="n">
+        <x:f>IF(C8="","",(1/'Metadata'!$B$5)^(C8-1))</x:f>
+        <x:v>204.17379446695296</x:v>
+      </x:c>
       <x:c r="E8" s="31" t="n">
-        <x:v>4881.6432054599</x:v>
-      </x:c>
-      <x:c r="F8" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G8" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H8" s="32" t="n">
-        <x:f>IF(E8=0,"",I8/E8)</x:f>
-        <x:v>204.17379446695296</x:v>
-      </x:c>
-      <x:c r="I8" s="31" t="n">
-        <x:f>IF(C8=0,"",SUMIF('Species'!$G$2:$G$67,A8,'Species'!$U$2:$U$67))</x:f>
+        <x:f>IF(B8=0,"",B8*D8)</x:f>
         <x:v>996703.616492567</x:v>
-      </x:c>
-      <x:c r="J8" s="32" t="n">
-        <x:v>3.31</x:v>
-      </x:c>
-      <x:c r="K8" s="32" t="n">
-        <x:f>IF(J8="","",(1/'Metadata'!$B$5)^(J8-1))</x:f>
-        <x:v>204.17379446695296</x:v>
-      </x:c>
-      <x:c r="L8" s="31" t="n">
-        <x:f>IF(E8=0,"",E8*K8)</x:f>
-        <x:v>996703.616492567</x:v>
-      </x:c>
-      <x:c r="M8" s="31" t="n">
-        <x:f>IF(E8=0,"",I8-L8)</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="N8" s="32" t="n">
-        <x:f>IF(L8=0,"",I8/L8)</x:f>
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="O8" s="34" t="n">
-        <x:f>IF(L8=0,"",M8/L8)</x:f>
-        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="9" ht="18" customHeight="1">
       <x:c r="A9" s="24" t="str">
         <x:v>Medium demersals (30 - 89 cm)</x:v>
       </x:c>
-      <x:c r="B9" s="33" t="n">
-        <x:v>6</x:v>
-      </x:c>
-      <x:c r="C9" s="33" t="n">
-        <x:v>6</x:v>
-      </x:c>
-      <x:c r="D9" s="31" t="n">
+      <x:c r="B9" s="31" t="n">
         <x:v>40151.7559930885</x:v>
       </x:c>
+      <x:c r="C9" s="32" t="n">
+        <x:v>3.4715593312226862</x:v>
+      </x:c>
+      <x:c r="D9" s="32" t="n">
+        <x:f>IF(C9="","",(1/'Metadata'!$B$5)^(C9-1))</x:f>
+        <x:v>296.1824567979166</x:v>
+      </x:c>
       <x:c r="E9" s="31" t="n">
-        <x:v>40151.7559930885</x:v>
-      </x:c>
-      <x:c r="F9" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G9" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H9" s="32" t="n">
-        <x:f>IF(E9=0,"",I9/E9)</x:f>
-        <x:v>363.5211410837258</x:v>
-      </x:c>
-      <x:c r="I9" s="31" t="n">
-        <x:f>IF(C9=0,"",SUMIF('Species'!$G$2:$G$67,A9,'Species'!$U$2:$U$67))</x:f>
-        <x:v>14596012.15512286</x:v>
-      </x:c>
-      <x:c r="J9" s="32" t="n">
-        <x:v>3.4715593312226862</x:v>
-      </x:c>
-      <x:c r="K9" s="32" t="n">
-        <x:f>IF(J9="","",(1/'Metadata'!$B$5)^(J9-1))</x:f>
-        <x:v>296.1824567979166</x:v>
-      </x:c>
-      <x:c r="L9" s="31" t="n">
-        <x:f>IF(E9=0,"",E9*K9)</x:f>
+        <x:f>IF(B9=0,"",B9*D9)</x:f>
         <x:v>11892245.734783424</x:v>
-      </x:c>
-      <x:c r="M9" s="31" t="n">
-        <x:f>IF(E9=0,"",I9-L9)</x:f>
-        <x:v>2703766.4203394353</x:v>
-      </x:c>
-      <x:c r="N9" s="32" t="n">
-        <x:f>IF(L9=0,"",I9/L9)</x:f>
-        <x:v>1.227355411302277</x:v>
-      </x:c>
-      <x:c r="O9" s="34" t="n">
-        <x:f>IF(L9=0,"",M9/L9)</x:f>
-        <x:v>0.22735541130227704</x:v>
       </x:c>
     </x:row>
     <x:row r="10" ht="18" customHeight="1">
       <x:c r="A10" s="24" t="str">
         <x:v>Medium pelagics (30 - 89 cm)</x:v>
       </x:c>
-      <x:c r="B10" s="33" t="n">
-        <x:v>8</x:v>
-      </x:c>
-      <x:c r="C10" s="33" t="n">
-        <x:v>8</x:v>
-      </x:c>
-      <x:c r="D10" s="31" t="n">
+      <x:c r="B10" s="31" t="n">
         <x:v>35509.5338734843</x:v>
       </x:c>
+      <x:c r="C10" s="32" t="n">
+        <x:v>4.095430604938611</x:v>
+      </x:c>
+      <x:c r="D10" s="32" t="n">
+        <x:f>IF(C10="","",(1/'Metadata'!$B$5)^(C10-1))</x:f>
+        <x:v>1245.7491655566569</x:v>
+      </x:c>
       <x:c r="E10" s="31" t="n">
-        <x:v>35509.5338734843</x:v>
-      </x:c>
-      <x:c r="F10" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G10" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H10" s="32" t="n">
-        <x:f>IF(E10=0,"",I10/E10)</x:f>
-        <x:v>1366.4699350269366</x:v>
-      </x:c>
-      <x:c r="I10" s="31" t="n">
-        <x:f>IF(C10=0,"",SUMIF('Species'!$G$2:$G$67,A10,'Species'!$U$2:$U$67))</x:f>
-        <x:v>48522710.4449369</x:v>
-      </x:c>
-      <x:c r="J10" s="32" t="n">
-        <x:v>4.095430604938611</x:v>
-      </x:c>
-      <x:c r="K10" s="32" t="n">
-        <x:f>IF(J10="","",(1/'Metadata'!$B$5)^(J10-1))</x:f>
-        <x:v>1245.7491655566569</x:v>
-      </x:c>
-      <x:c r="L10" s="31" t="n">
-        <x:f>IF(E10=0,"",E10*K10)</x:f>
+        <x:f>IF(B10=0,"",B10*D10)</x:f>
         <x:v>44235972.19219891</x:v>
-      </x:c>
-      <x:c r="M10" s="31" t="n">
-        <x:f>IF(E10=0,"",I10-L10)</x:f>
-        <x:v>4286738.2527379915</x:v>
-      </x:c>
-      <x:c r="N10" s="32" t="n">
-        <x:f>IF(L10=0,"",I10/L10)</x:f>
-        <x:v>1.0969061612145141</x:v>
-      </x:c>
-      <x:c r="O10" s="34" t="n">
-        <x:f>IF(L10=0,"",M10/L10)</x:f>
-        <x:v>0.09690616121451413</x:v>
       </x:c>
     </x:row>
     <x:row r="11" ht="18" customHeight="1">
       <x:c r="A11" s="24" t="str">
         <x:v>Medium reef assoc. fish (30 - 89 cm)</x:v>
       </x:c>
-      <x:c r="B11" s="33" t="n">
-        <x:v>8</x:v>
-      </x:c>
-      <x:c r="C11" s="33" t="n">
-        <x:v>8</x:v>
-      </x:c>
-      <x:c r="D11" s="31" t="n">
+      <x:c r="B11" s="31" t="n">
         <x:v>10038.161370280599</x:v>
       </x:c>
+      <x:c r="C11" s="32" t="n">
+        <x:v>3.4625998688545003</x:v>
+      </x:c>
+      <x:c r="D11" s="32" t="n">
+        <x:f>IF(C11="","",(1/'Metadata'!$B$5)^(C11-1))</x:f>
+        <x:v>290.1348305992465</x:v>
+      </x:c>
       <x:c r="E11" s="31" t="n">
-        <x:v>10038.161370280599</x:v>
-      </x:c>
-      <x:c r="F11" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G11" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H11" s="32" t="n">
-        <x:f>IF(E11=0,"",I11/E11)</x:f>
-        <x:v>696.1529738487621</x:v>
-      </x:c>
-      <x:c r="I11" s="31" t="n">
-        <x:f>IF(C11=0,"",SUMIF('Species'!$G$2:$G$67,A11,'Species'!$U$2:$U$67))</x:f>
-        <x:v>6988095.889894605</x:v>
-      </x:c>
-      <x:c r="J11" s="32" t="n">
-        <x:v>3.4625998688545003</x:v>
-      </x:c>
-      <x:c r="K11" s="32" t="n">
-        <x:f>IF(J11="","",(1/'Metadata'!$B$5)^(J11-1))</x:f>
-        <x:v>290.1348305992465</x:v>
-      </x:c>
-      <x:c r="L11" s="31" t="n">
-        <x:f>IF(E11=0,"",E11*K11)</x:f>
+        <x:f>IF(B11=0,"",B11*D11)</x:f>
         <x:v>2912420.248694262</x:v>
-      </x:c>
-      <x:c r="M11" s="31" t="n">
-        <x:f>IF(E11=0,"",I11-L11)</x:f>
-        <x:v>4075675.6412003427</x:v>
-      </x:c>
-      <x:c r="N11" s="32" t="n">
-        <x:f>IF(L11=0,"",I11/L11)</x:f>
-        <x:v>2.3994119300013823</x:v>
-      </x:c>
-      <x:c r="O11" s="34" t="n">
-        <x:f>IF(L11=0,"",M11/L11)</x:f>
-        <x:v>1.399411930001382</x:v>
       </x:c>
     </x:row>
     <x:row r="12" ht="18" customHeight="1">
       <x:c r="A12" s="24" t="str">
         <x:v>Other demersal invertebrates</x:v>
       </x:c>
-      <x:c r="B12" s="33" t="n">
+      <x:c r="B12" s="31" t="n">
+        <x:v>15.6414576048</x:v>
+      </x:c>
+      <x:c r="C12" s="32" t="n">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="C12" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="D12" s="31" t="n">
-        <x:v>15.6414576048</x:v>
+      <x:c r="D12" s="32" t="n">
+        <x:f>IF(C12="","",(1/'Metadata'!$B$5)^(C12-1))</x:f>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="E12" s="31" t="n">
-        <x:v>15.6414576048</x:v>
-      </x:c>
-      <x:c r="F12" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G12" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H12" s="32" t="n">
-        <x:f>IF(E12=0,"",I12/E12)</x:f>
-        <x:v>10.000000000000002</x:v>
-      </x:c>
-      <x:c r="I12" s="31" t="n">
-        <x:f>IF(C12=0,"",SUMIF('Species'!$G$2:$G$67,A12,'Species'!$U$2:$U$67))</x:f>
-        <x:v>156.41457604800001</x:v>
-      </x:c>
-      <x:c r="J12" s="32" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="K12" s="32" t="n">
-        <x:f>IF(J12="","",(1/'Metadata'!$B$5)^(J12-1))</x:f>
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="L12" s="31" t="n">
-        <x:f>IF(E12=0,"",E12*K12)</x:f>
+        <x:f>IF(B12=0,"",B12*D12)</x:f>
         <x:v>156.414576048</x:v>
-      </x:c>
-      <x:c r="M12" s="31" t="n">
-        <x:f>IF(E12=0,"",I12-L12)</x:f>
-        <x:v>2.842170943040401e-14</x:v>
-      </x:c>
-      <x:c r="N12" s="32" t="n">
-        <x:f>IF(L12=0,"",I12/L12)</x:f>
-        <x:v>1.0000000000000002</x:v>
-      </x:c>
-      <x:c r="O12" s="34" t="n">
-        <x:f>IF(L12=0,"",M12/L12)</x:f>
-        <x:v>1.8170755020735438e-16</x:v>
       </x:c>
     </x:row>
     <x:row r="13" ht="18" customHeight="1">
       <x:c r="A13" s="24" t="str">
         <x:v>Shrimps</x:v>
       </x:c>
-      <x:c r="B13" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="C13" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="D13" s="31" t="n">
+      <x:c r="B13" s="31" t="n">
         <x:v>530.6444829110001</x:v>
       </x:c>
+      <x:c r="C13" s="32" t="n">
+        <x:v>3.1960289016030483</x:v>
+      </x:c>
+      <x:c r="D13" s="32" t="n">
+        <x:f>IF(C13="","",(1/'Metadata'!$B$5)^(C13-1))</x:f>
+        <x:v>157.04673129435403</x:v>
+      </x:c>
       <x:c r="E13" s="31" t="n">
-        <x:v>530.6444829110001</x:v>
-      </x:c>
-      <x:c r="F13" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G13" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H13" s="32" t="n">
-        <x:f>IF(E13=0,"",I13/E13)</x:f>
-        <x:v>175.39047370077415</x:v>
-      </x:c>
-      <x:c r="I13" s="31" t="n">
-        <x:f>IF(C13=0,"",SUMIF('Species'!$G$2:$G$67,A13,'Species'!$U$2:$U$67))</x:f>
-        <x:v>93069.98722446266</x:v>
-      </x:c>
-      <x:c r="J13" s="32" t="n">
-        <x:v>3.1960289016030483</x:v>
-      </x:c>
-      <x:c r="K13" s="32" t="n">
-        <x:f>IF(J13="","",(1/'Metadata'!$B$5)^(J13-1))</x:f>
-        <x:v>157.04673129435403</x:v>
-      </x:c>
-      <x:c r="L13" s="31" t="n">
-        <x:f>IF(E13=0,"",E13*K13)</x:f>
+        <x:f>IF(B13=0,"",B13*D13)</x:f>
         <x:v>83335.98152055527</x:v>
-      </x:c>
-      <x:c r="M13" s="31" t="n">
-        <x:f>IF(E13=0,"",I13-L13)</x:f>
-        <x:v>9734.005703907387</x:v>
-      </x:c>
-      <x:c r="N13" s="32" t="n">
-        <x:f>IF(L13=0,"",I13/L13)</x:f>
-        <x:v>1.116804356609233</x:v>
-      </x:c>
-      <x:c r="O13" s="34" t="n">
-        <x:f>IF(L13=0,"",M13/L13)</x:f>
-        <x:v>0.11680435660923297</x:v>
       </x:c>
     </x:row>
     <x:row r="14" ht="18" customHeight="1">
       <x:c r="A14" s="24" t="str">
         <x:v>Small demersals (&lt;30 cm)</x:v>
       </x:c>
-      <x:c r="B14" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C14" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="D14" s="31" t="n">
+      <x:c r="B14" s="31" t="n">
         <x:v>557.9877797652</x:v>
       </x:c>
+      <x:c r="C14" s="32" t="n">
+        <x:v>3.51</x:v>
+      </x:c>
+      <x:c r="D14" s="32" t="n">
+        <x:f>IF(C14="","",(1/'Metadata'!$B$5)^(C14-1))</x:f>
+        <x:v>323.5936569296281</x:v>
+      </x:c>
       <x:c r="E14" s="31" t="n">
-        <x:v>557.9877797652</x:v>
-      </x:c>
-      <x:c r="F14" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G14" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H14" s="32" t="n">
-        <x:f>IF(E14=0,"",I14/E14)</x:f>
-        <x:v>323.5936569296281</x:v>
-      </x:c>
-      <x:c r="I14" s="31" t="n">
-        <x:f>IF(C14=0,"",SUMIF('Species'!$G$2:$G$67,A14,'Species'!$U$2:$U$67))</x:f>
+        <x:f>IF(B14=0,"",B14*D14)</x:f>
         <x:v>180561.306176265</x:v>
-      </x:c>
-      <x:c r="J14" s="32" t="n">
-        <x:v>3.51</x:v>
-      </x:c>
-      <x:c r="K14" s="32" t="n">
-        <x:f>IF(J14="","",(1/'Metadata'!$B$5)^(J14-1))</x:f>
-        <x:v>323.5936569296281</x:v>
-      </x:c>
-      <x:c r="L14" s="31" t="n">
-        <x:f>IF(E14=0,"",E14*K14)</x:f>
-        <x:v>180561.306176265</x:v>
-      </x:c>
-      <x:c r="M14" s="31" t="n">
-        <x:f>IF(E14=0,"",I14-L14)</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="N14" s="32" t="n">
-        <x:f>IF(L14=0,"",I14/L14)</x:f>
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="O14" s="34" t="n">
-        <x:f>IF(L14=0,"",M14/L14)</x:f>
-        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="15" ht="18" customHeight="1">
       <x:c r="A15" s="24" t="str">
         <x:v>Small pelagics (&lt;30 cm)</x:v>
       </x:c>
-      <x:c r="B15" s="33" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="C15" s="33" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="D15" s="31" t="n">
+      <x:c r="B15" s="31" t="n">
         <x:v>155986.16996456447</x:v>
       </x:c>
+      <x:c r="C15" s="32" t="n">
+        <x:v>2.517198299055919</x:v>
+      </x:c>
+      <x:c r="D15" s="32" t="n">
+        <x:f>IF(C15="","",(1/'Metadata'!$B$5)^(C15-1))</x:f>
+        <x:v>32.900181896402685</x:v>
+      </x:c>
       <x:c r="E15" s="31" t="n">
-        <x:v>155986.16996456447</x:v>
-      </x:c>
-      <x:c r="F15" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G15" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H15" s="32" t="n">
-        <x:f>IF(E15=0,"",I15/E15)</x:f>
-        <x:v>43.17829767383648</x:v>
-      </x:c>
-      <x:c r="I15" s="31" t="n">
-        <x:f>IF(C15=0,"",SUMIF('Species'!$G$2:$G$67,A15,'Species'!$U$2:$U$67))</x:f>
-        <x:v>6735217.279731616</x:v>
-      </x:c>
-      <x:c r="J15" s="32" t="n">
-        <x:v>2.517198299055919</x:v>
-      </x:c>
-      <x:c r="K15" s="32" t="n">
-        <x:f>IF(J15="","",(1/'Metadata'!$B$5)^(J15-1))</x:f>
-        <x:v>32.900181896402685</x:v>
-      </x:c>
-      <x:c r="L15" s="31" t="n">
-        <x:f>IF(E15=0,"",E15*K15)</x:f>
+        <x:f>IF(B15=0,"",B15*D15)</x:f>
         <x:v>5131973.3651573565</x:v>
-      </x:c>
-      <x:c r="M15" s="31" t="n">
-        <x:f>IF(E15=0,"",I15-L15)</x:f>
-        <x:v>1603243.91457426</x:v>
-      </x:c>
-      <x:c r="N15" s="32" t="n">
-        <x:f>IF(L15=0,"",I15/L15)</x:f>
-        <x:v>1.3124030076732678</x:v>
-      </x:c>
-      <x:c r="O15" s="34" t="n">
-        <x:f>IF(L15=0,"",M15/L15)</x:f>
-        <x:v>0.31240300767326784</x:v>
       </x:c>
     </x:row>
     <x:row r="16" ht="18" customHeight="1">
       <x:c r="A16" s="24" t="str">
         <x:v>Small reef assoc. fish (&lt;30 cm)</x:v>
       </x:c>
-      <x:c r="B16" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C16" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="D16" s="31" t="n">
+      <x:c r="B16" s="31" t="n">
         <x:v>3999.6632556148998</x:v>
       </x:c>
+      <x:c r="C16" s="32" t="n">
+        <x:v>2.76</x:v>
+      </x:c>
+      <x:c r="D16" s="32" t="n">
+        <x:f>IF(C16="","",(1/'Metadata'!$B$5)^(C16-1))</x:f>
+        <x:v>57.543993733715666</x:v>
+      </x:c>
       <x:c r="E16" s="31" t="n">
-        <x:v>3999.6632556148998</x:v>
-      </x:c>
-      <x:c r="F16" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G16" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H16" s="32" t="n">
-        <x:f>IF(E16=0,"",I16/E16)</x:f>
-        <x:v>57.543993733715666</x:v>
-      </x:c>
-      <x:c r="I16" s="31" t="n">
-        <x:f>IF(C16=0,"",SUMIF('Species'!$G$2:$G$67,A16,'Species'!$U$2:$U$67))</x:f>
+        <x:f>IF(B16=0,"",B16*D16)</x:f>
         <x:v>230156.5973180766</x:v>
-      </x:c>
-      <x:c r="J16" s="32" t="n">
-        <x:v>2.76</x:v>
-      </x:c>
-      <x:c r="K16" s="32" t="n">
-        <x:f>IF(J16="","",(1/'Metadata'!$B$5)^(J16-1))</x:f>
-        <x:v>57.543993733715666</x:v>
-      </x:c>
-      <x:c r="L16" s="31" t="n">
-        <x:f>IF(E16=0,"",E16*K16)</x:f>
-        <x:v>230156.5973180766</x:v>
-      </x:c>
-      <x:c r="M16" s="31" t="n">
-        <x:f>IF(E16=0,"",I16-L16)</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="N16" s="32" t="n">
-        <x:f>IF(L16=0,"",I16/L16)</x:f>
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="O16" s="34" t="n">
-        <x:f>IF(L16=0,"",M16/L16)</x:f>
-        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="17" ht="18" customHeight="1">
       <x:c r="A17" s="24" t="str">
         <x:v>Small to medium sharks (&lt;90 cm)</x:v>
       </x:c>
-      <x:c r="B17" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C17" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="D17" s="31" t="n">
+      <x:c r="B17" s="31" t="n">
         <x:v>0.1204771814</x:v>
       </x:c>
+      <x:c r="C17" s="32" t="n">
+        <x:v>3.9</x:v>
+      </x:c>
+      <x:c r="D17" s="32" t="n">
+        <x:f>IF(C17="","",(1/'Metadata'!$B$5)^(C17-1))</x:f>
+        <x:v>794.3282347242813</x:v>
+      </x:c>
       <x:c r="E17" s="31" t="n">
-        <x:v>0.1204771814</x:v>
-      </x:c>
-      <x:c r="F17" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G17" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H17" s="32" t="n">
-        <x:f>IF(E17=0,"",I17/E17)</x:f>
-        <x:v>794.3282347242813</x:v>
-      </x:c>
-      <x:c r="I17" s="31" t="n">
-        <x:f>IF(C17=0,"",SUMIF('Species'!$G$2:$G$67,A17,'Species'!$U$2:$U$67))</x:f>
+        <x:f>IF(B17=0,"",B17*D17)</x:f>
         <x:v>95.69842682601902</x:v>
       </x:c>
-      <x:c r="J17" s="32" t="n">
-        <x:v>3.9</x:v>
-      </x:c>
-      <x:c r="K17" s="32" t="n">
-        <x:f>IF(J17="","",(1/'Metadata'!$B$5)^(J17-1))</x:f>
-        <x:v>794.3282347242813</x:v>
-      </x:c>
-      <x:c r="L17" s="31" t="n">
-        <x:f>IF(E17=0,"",E17*K17)</x:f>
-        <x:v>95.69842682601902</x:v>
-      </x:c>
-      <x:c r="M17" s="31" t="n">
-        <x:f>IF(E17=0,"",I17-L17)</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="N17" s="32" t="n">
-        <x:f>IF(L17=0,"",I17/L17)</x:f>
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="O17" s="34" t="n">
-        <x:f>IF(L17=0,"",M17/L17)</x:f>
-        <x:v>0</x:v>
-      </x:c>
     </x:row>
   </x:sheetData>
-  <x:conditionalFormatting sqref="G2:G17">
-    <x:cfRule type="cellIs" dxfId="2" priority="1" operator="lessThan">
-      <x:formula>0.9</x:formula>
-    </x:cfRule>
-  </x:conditionalFormatting>
-  <x:conditionalFormatting sqref="O2:O17">
-    <x:cfRule type="dataBar" priority="2">
-      <x:dataBar>
-        <x:cfvo type="min"/>
-        <x:cfvo type="max"/>
-        <x:color rgb="FFE28A32"/>
-      </x:dataBar>
-    </x:cfRule>
-  </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R240086c3c31143ec"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R6cad1d2395c544b0"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -6767,7 +5773,7 @@
       <x:c r="B5" s="24" t="str">
         <x:v>catch_reconciled</x:v>
       </x:c>
-      <x:c r="C5" s="35" t="b">
+      <x:c r="C5" s="33" t="b">
         <x:v>1</x:v>
       </x:c>
       <x:c r="D5" s="24" t="str">
@@ -6866,7 +5872,7 @@
         <x:v>commercial_ppr</x:v>
       </x:c>
       <x:c r="C12" s="24" t="n">
-        <x:v>187008419.87587017</x:v>
+        <x:v>157417671.79835263</x:v>
       </x:c>
       <x:c r="D12" s="24" t="str">
         <x:v>tonnes_primary_production_equivalent</x:v>
@@ -6880,7 +5886,7 @@
         <x:v>functional_ppr</x:v>
       </x:c>
       <x:c r="C13" s="24" t="n">
-        <x:v>187008419.87587017</x:v>
+        <x:v>173471533.90377143</x:v>
       </x:c>
       <x:c r="D13" s="24" t="str">
         <x:v>tonnes_primary_production_equivalent</x:v>
@@ -6894,7 +5900,7 @@
         <x:v>commercial_ppr_difference</x:v>
       </x:c>
       <x:c r="C14" s="24" t="n">
-        <x:v>-5.960464477539063e-8</x:v>
+        <x:v>-29590748.0775176</x:v>
       </x:c>
       <x:c r="D14" s="24" t="str">
         <x:v>tonnes_primary_production_equivalent</x:v>
@@ -6908,7 +5914,7 @@
         <x:v>functional_ppr_difference</x:v>
       </x:c>
       <x:c r="C15" s="24" t="n">
-        <x:v>-5.960464477539063e-8</x:v>
+        <x:v>-13536885.972098798</x:v>
       </x:c>
       <x:c r="D15" s="24" t="str">
         <x:v>tonnes_primary_production_equivalent</x:v>
@@ -6919,9 +5925,9 @@
         <x:v>EEZ_512</x:v>
       </x:c>
       <x:c r="B16" s="24" t="str">
-        <x:v>commercial_ppr_reconciled</x:v>
-      </x:c>
-      <x:c r="C16" s="35" t="b">
+        <x:v>tl_coverage_complete</x:v>
+      </x:c>
+      <x:c r="C16" s="33" t="b">
         <x:v>1</x:v>
       </x:c>
       <x:c r="D16" s="24" t="str">
@@ -6933,47 +5939,19 @@
         <x:v>EEZ_512</x:v>
       </x:c>
       <x:c r="B17" s="24" t="str">
-        <x:v>functional_ppr_reconciled</x:v>
-      </x:c>
-      <x:c r="C17" s="35" t="b">
+        <x:v>group_ppr_within_convexity_bound</x:v>
+      </x:c>
+      <x:c r="C17" s="33" t="b">
         <x:v>1</x:v>
       </x:c>
       <x:c r="D17" s="24" t="str">
         <x:v>boolean</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="18" ht="18" customHeight="1">
-      <x:c r="A18" s="24" t="str">
-        <x:v>EEZ_512</x:v>
-      </x:c>
-      <x:c r="B18" s="24" t="str">
-        <x:v>commercial_jensen_violations</x:v>
-      </x:c>
-      <x:c r="C18" s="24" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="D18" s="24" t="str">
-        <x:v>count</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="19" ht="18" customHeight="1">
-      <x:c r="A19" s="24" t="str">
-        <x:v>EEZ_512</x:v>
-      </x:c>
-      <x:c r="B19" s="24" t="str">
-        <x:v>functional_jensen_violations</x:v>
-      </x:c>
-      <x:c r="C19" s="24" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="D19" s="24" t="str">
-        <x:v>count</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R27fd457af8344836"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R1823f8ac14b949fc"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -7020,7 +5998,7 @@
       <x:c r="A5" s="22" t="str">
         <x:v>Transfer efficiency</x:v>
       </x:c>
-      <x:c r="B5" s="36" t="n">
+      <x:c r="B5" s="34" t="n">
         <x:v>0.1</x:v>
       </x:c>
       <x:c r="C5" s="18" t="str">
